--- a/artfynd/A 41568-2025 artfynd.xlsx
+++ b/artfynd/A 41568-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127735628</v>
       </c>
       <c r="B2" t="n">
-        <v>97351</v>
+        <v>97352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127735627</v>
       </c>
       <c r="B3" t="n">
-        <v>97351</v>
+        <v>97352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41568-2025 artfynd.xlsx
+++ b/artfynd/A 41568-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127735628</v>
       </c>
       <c r="B2" t="n">
-        <v>97352</v>
+        <v>97353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127735627</v>
       </c>
       <c r="B3" t="n">
-        <v>97352</v>
+        <v>97353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41568-2025 artfynd.xlsx
+++ b/artfynd/A 41568-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127735628</v>
       </c>
       <c r="B2" t="n">
-        <v>97353</v>
+        <v>97361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127735627</v>
       </c>
       <c r="B3" t="n">
-        <v>97353</v>
+        <v>97361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41568-2025 artfynd.xlsx
+++ b/artfynd/A 41568-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127735628</v>
       </c>
       <c r="B2" t="n">
-        <v>97361</v>
+        <v>97454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127735627</v>
       </c>
       <c r="B3" t="n">
-        <v>97361</v>
+        <v>97454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41568-2025 artfynd.xlsx
+++ b/artfynd/A 41568-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127735628</v>
+        <v>127735627</v>
       </c>
       <c r="B2" t="n">
-        <v>97454</v>
+        <v>97989</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570068</v>
+        <v>570077</v>
       </c>
       <c r="R2" t="n">
-        <v>6719297</v>
+        <v>6719289</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127735627</v>
+        <v>127735628</v>
       </c>
       <c r="B3" t="n">
-        <v>97454</v>
+        <v>97989</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570077</v>
+        <v>570068</v>
       </c>
       <c r="R3" t="n">
-        <v>6719289</v>
+        <v>6719297</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
